--- a/backend/app/agent_artifacts/templates/campaign_report_v2.xlsx
+++ b/backend/app/agent_artifacts/templates/campaign_report_v2.xlsx
@@ -16,10 +16,9 @@
     <sheet name="自然传播与受众" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="洞察与建议" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="方法论" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ROI与转化" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="TEMPLATE_VERSION">'活动综合概览'!$A$1000</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -457,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -485,17 +484,49 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
     </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr">
-        <is>
-          <t>gate-c-v1</t>
-        </is>
-      </c>
-      <c r="B1000" t="inlineStr">
-        <is>
-          <t>template_version</t>
-        </is>
-      </c>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ROI与转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
